--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
+        <v>98048</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98048</v>
+        <v>98050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98050</v>
+        <v>98057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98057</v>
+        <v>98066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98066</v>
+        <v>98074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98074</v>
+        <v>98076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54197-2022 artfynd.xlsx
+++ b/artfynd/A 54197-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121991018</v>
       </c>
       <c r="B2" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
